--- a/Benchmark/Bencmarks Table&Chart.xlsx
+++ b/Benchmark/Bencmarks Table&Chart.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amir\University\Term 3\First Project\project01-unidb-ahk1384\Benchmark\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:10000001_{4DD90BF9-D47F-4CEA-94BD-D33C05D420BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:10000001_{A9FB6EFE-8EAA-402D-80E9-3219B96617C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14889" activeTab="2" xr2:uid="{11FA89B9-BB10-4E01-82E6-D72B32334542}"/>
   </bookViews>
@@ -20489,6 +20489,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03996659-6491-4A68-BAC9-7ADEE61E324C}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A7:E9"/>
   <sheetFormatPr defaultRowHeight="13.6" x14ac:dyDescent="0.2"/>
   <cols>
@@ -20556,8 +20559,8 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" r:id="rId1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="53" orientation="landscape" horizontalDpi="300" r:id="rId1"/>
   <drawing r:id="rId2"/>
   <tableParts count="1">
     <tablePart r:id="rId3"/>
